--- a/artfynd/A 6923-2023 artfynd.xlsx
+++ b/artfynd/A 6923-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,268 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125419763</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nya gläntan, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>546924</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6475937</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Törnevalla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Del i ett projekt kopplat till medborgarforskning med skolelever. Observation gjord med appen Merlin.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kråka Larsen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kråka Larsen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Projekt Avalon</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125419739</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58158</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nya gläntan, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546924</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6475937</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Törnevalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Del i ett projekt kopplat till medborgarforskning med skolelever. Observation gjord med appen Merlin.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kråka Larsen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kråka Larsen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Projekt Avalon</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6923-2023 artfynd.xlsx
+++ b/artfynd/A 6923-2023 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125419763</v>
+        <v>125419729</v>
       </c>
       <c r="B3" t="n">
         <v>57761</v>

--- a/artfynd/A 6923-2023 artfynd.xlsx
+++ b/artfynd/A 6923-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124688555</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125419729</v>
+        <v>125419763</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>125419739</v>
       </c>
       <c r="B4" t="n">
-        <v>58158</v>
+        <v>58272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 6923-2023 artfynd.xlsx
+++ b/artfynd/A 6923-2023 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125419763</v>
+        <v>125419729</v>
       </c>
       <c r="B3" t="n">
         <v>57914</v>

--- a/artfynd/A 6923-2023 artfynd.xlsx
+++ b/artfynd/A 6923-2023 artfynd.xlsx
@@ -797,15 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125419729</v>
+        <v>125419763</v>
       </c>
       <c r="B3" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,12 +926,7 @@
         <v>125419739</v>
       </c>
       <c r="B4" t="n">
-        <v>58272</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6923-2023 artfynd.xlsx
+++ b/artfynd/A 6923-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>125419763</v>
       </c>
       <c r="B3" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>125419739</v>
       </c>
       <c r="B4" t="n">
-        <v>58291</v>
+        <v>58292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
